--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:07</t>
+    <t xml:space="preserve">2026-09-09 23:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:00</t>
+    <t xml:space="preserve">2026-09-17 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:58</t>
+    <t xml:space="preserve">2026-09-23 12:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:27</t>
+    <t xml:space="preserve">2026-10-02 13:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_nuble.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Quillón</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Treguaco</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:23</t>
+    <t xml:space="preserve">2026-10-04 08:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:47</t>
+    <t xml:space="preserve">2026-10-05 10:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -578,7 +578,7 @@
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>628122.12</v>
+        <v>628122.13</v>
       </c>
     </row>
     <row r="5">
